--- a/Propulsion & Power/Tabulated Airfoil c_d Values/NACA2412_c_d.xlsx
+++ b/Propulsion & Power/Tabulated Airfoil c_d Values/NACA2412_c_d.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/arvkb9_umsystem_edu/Documents/896 - B.S Aerospace Engineering Courses/92 - Fall 2026/6 - AE4780-Meeks/Github Repo/AE4780-Meeks/Tabulated Airfoil c_d Values/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/arvkb9_umsystem_edu/Documents/896 - B.S Aerospace Engineering Courses/92 - Fall 2026/6 - AE4780-Meeks/Github Repo/Miner-Works-MW-27-MantaRay/Propulsion &amp; Power/Tabulated Airfoil c_d Values/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{C8331AD9-2580-4981-A1BF-8B38E094E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E6EC353-C4C8-432E-BEC6-26DE7BE0F6E9}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{C8331AD9-2580-4981-A1BF-8B38E094E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361EE317-841E-4109-8A58-C81F0DE5EEB5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{1B61AF13-B459-4C3D-BF8D-2C9191432F03}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1B61AF13-B459-4C3D-BF8D-2C9191432F03}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -528,8 +528,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
@@ -906,10 +905,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBA682F-1EE0-4690-839E-BA65C1D4FED7}">
-  <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -917,308 +916,252 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>-5</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>1.281E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>-4.5</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>1.191E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>-4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>1.1129999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>-3.5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>1.0019999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>-3</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>9.41E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>-2.5</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>8.9800000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>-2</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>8.5299999999999994E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>-1.5</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>8.2000000000000007E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>-1</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>7.8499999999999993E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>-0.5</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <v>7.5599999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>0</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <v>7.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>0.5</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14">
         <v>7.0600000000000003E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>1.5</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <v>7.3699999999999998E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
         <v>7.79E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>2.5</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
         <v>7.9299999999999995E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>3</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18">
         <v>8.2500000000000004E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>3.5</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>8.6599999999999993E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>4</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20">
         <v>8.9200000000000008E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>4.5</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21">
         <v>9.5999999999999992E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>5</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22">
         <v>1.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>5.5</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23">
         <v>1.1809999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>6</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24">
         <v>1.3849999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>6.5</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25">
         <v>1.468E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>7</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26">
         <v>1.5689999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>7.5</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27">
         <v>1.687E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>8</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28">
         <v>1.787E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>8.5</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29">
         <v>1.9089999999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>9</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30">
         <v>1.9890000000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>9.5</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31">
         <v>2.0080000000000001E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>10</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32">
         <v>2.1440000000000001E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>10.5</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2.3640000000000001E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>11</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2.6620000000000001E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>23</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.32233000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>23.5</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.33283000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>24</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.34255999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>24.5</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.35058</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>25</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.33524999999999999</v>
       </c>
     </row>
   </sheetData>
